--- a/output/pdf_financials_xlsx/PAU.xlsx
+++ b/output/pdf_financials_xlsx/PAU.xlsx
@@ -474,20 +474,14 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -496,20 +490,14 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -518,20 +506,14 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -540,20 +522,14 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.456976</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.64536</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1.243419</v>
       </c>
     </row>
     <row r="8">
@@ -562,20 +538,14 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -584,20 +554,14 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -606,20 +570,14 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.456976</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.64536</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1.243419</v>
       </c>
     </row>
     <row r="11">
@@ -628,20 +586,14 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.735793</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-1.149977</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-2.348615</v>
       </c>
     </row>
     <row r="12">
@@ -650,20 +602,14 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -672,20 +618,14 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -694,20 +634,14 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -716,20 +650,14 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>-0.008692999999999999</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-0.035172</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-0.003325</v>
       </c>
     </row>
     <row r="16">
@@ -738,20 +666,14 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-1.182098</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-1.472107</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-2.351049</v>
       </c>
     </row>
     <row r="17">
@@ -760,20 +682,14 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -826,20 +742,14 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-1.182098</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-1.472107</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-2.351049</v>
       </c>
     </row>
     <row r="21">
@@ -848,20 +758,14 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -870,20 +774,14 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -892,20 +790,14 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-1.182098</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-1.472107</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-2.351049</v>
       </c>
     </row>
     <row r="24">
@@ -930,20 +822,14 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="26">
@@ -962,10 +848,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D26" s="3" t="n">
+        <v>117.55245</v>
       </c>
     </row>
     <row r="27">
@@ -974,20 +858,14 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-1.182098</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-1.472107</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-2.351049</v>
       </c>
     </row>
     <row r="28">
@@ -996,20 +874,14 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1018,20 +890,14 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-1.182098</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-1.472107</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-2.351049</v>
       </c>
     </row>
     <row r="30">
@@ -1062,20 +928,14 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1129,20 +989,14 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1151,20 +1005,14 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.263214</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>2.56753</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>3.969579</v>
       </c>
     </row>
     <row r="37">
@@ -1173,20 +1021,14 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1195,20 +1037,14 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1217,20 +1053,14 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1239,20 +1069,14 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1277,20 +1101,14 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1299,20 +1117,14 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1321,20 +1133,14 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1343,20 +1149,14 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1365,20 +1165,14 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1387,20 +1181,14 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1409,20 +1197,14 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.004974</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.006957</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.09893299999999999</v>
       </c>
     </row>
     <row r="49">
@@ -1447,20 +1229,14 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1469,20 +1245,14 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1491,20 +1261,14 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1513,20 +1277,14 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1535,20 +1293,14 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1579,20 +1331,14 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1601,20 +1347,14 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1623,20 +1363,14 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>2.686968</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>4.212197</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>8.904588</v>
       </c>
     </row>
     <row r="59">
@@ -1645,20 +1379,14 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1667,20 +1395,14 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1689,20 +1411,14 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0.036685</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.036685</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0.061096</v>
       </c>
     </row>
     <row r="62">
@@ -1743,20 +1459,14 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1765,20 +1475,14 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1787,20 +1491,14 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1809,20 +1507,14 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1847,20 +1539,14 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0.0475</v>
       </c>
     </row>
     <row r="70">
@@ -1869,20 +1555,14 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1891,20 +1571,14 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0.0475</v>
       </c>
     </row>
     <row r="72">
@@ -1913,20 +1587,14 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1935,20 +1603,14 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1957,20 +1619,14 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1979,20 +1635,14 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2023,20 +1673,14 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2045,20 +1689,14 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2067,20 +1705,14 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2089,20 +1721,14 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.01651300303387321</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.007739562263393435</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.003746912839629054</v>
       </c>
     </row>
     <row r="81">
@@ -2111,20 +1737,14 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2133,20 +1753,14 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2155,20 +1769,14 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2177,20 +1785,14 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2199,20 +1801,14 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2259,20 +1855,14 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>8.486034999999999</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>12.761609</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>20.549168</v>
       </c>
     </row>
     <row r="89">
@@ -2281,20 +1871,14 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2319,20 +1903,14 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2357,20 +1935,14 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2395,20 +1967,14 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2417,20 +1983,14 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>2.876521</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>6.137298</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>12.677103</v>
       </c>
     </row>
     <row r="97">
@@ -2462,20 +2022,14 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-1.182098</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-1.472107</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-2.351049</v>
       </c>
     </row>
     <row r="100">
@@ -2484,20 +2038,14 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2506,20 +2054,14 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>-0.002588</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>-0.027712</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>-0.002935</v>
       </c>
     </row>
     <row r="102">
@@ -2528,20 +2070,14 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2550,20 +2086,14 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0.000974</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>-0.001983</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>-0.091976</v>
       </c>
     </row>
     <row r="104">
@@ -2588,20 +2118,14 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2610,20 +2134,14 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.009358999999999999</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.06565699999999999</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>-0.133564</v>
       </c>
     </row>
     <row r="107">
@@ -2648,20 +2166,14 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2670,20 +2182,14 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2692,20 +2198,14 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2714,20 +2214,14 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2736,20 +2230,14 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2758,20 +2246,14 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2780,20 +2262,14 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2802,20 +2278,14 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2824,20 +2294,14 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2846,20 +2310,14 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2868,20 +2326,14 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2906,20 +2358,14 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2928,20 +2374,14 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2950,20 +2390,14 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2972,20 +2406,14 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2994,20 +2422,14 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3016,20 +2438,14 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3038,20 +2454,14 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3082,20 +2492,14 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3136,20 +2540,14 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3158,20 +2556,14 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.122643</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>2.304316</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>1.402049</v>
       </c>
     </row>
     <row r="133">
@@ -3180,20 +2572,14 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.263214</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>2.56753</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>3.969579</v>
       </c>
     </row>
     <row r="134">
@@ -3202,20 +2588,14 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3224,20 +2604,14 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.51093</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-0.705492</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-1.546915</v>
       </c>
     </row>
   </sheetData>
@@ -3489,7 +2863,11 @@
           <t>Exploration and evaluation assets 3</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>2.686968</v>
       </c>
@@ -3609,7 +2987,11 @@
           <t>Loan payable 4</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>0.0475</v>
       </c>
@@ -3847,7 +3229,11 @@
           <t>Net loss for the year</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>-1.182098</v>
       </c>
@@ -3938,7 +3324,11 @@
           <t>Receivables</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>-0.002588</v>
       </c>
@@ -3965,7 +3355,11 @@
           <t>Prepaid expenses and deposits</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>0.000974</v>
       </c>
@@ -4263,7 +3657,11 @@
           <t>Change in cash during the year</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>-0.122643</v>
       </c>
@@ -4321,7 +3719,11 @@
           <t>Cash, end of the year</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>0.263214</v>
       </c>
@@ -4470,7 +3872,11 @@
           <t>Consulting and management fees 8</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>0.226075</v>
       </c>
@@ -4497,7 +3903,11 @@
           <t>Shareholder communications</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>0.19204</v>
       </c>
@@ -4586,7 +3996,11 @@
           <t>Regulatory transfer agent fees</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
         <v>0.031874</v>
       </c>
@@ -4613,7 +4027,11 @@
           <t>Travel</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
         <v>0.006987</v>
       </c>
@@ -4667,7 +4085,11 @@
           <t>Loss before other items</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
         <v>-0.735793</v>
       </c>
@@ -4694,7 +4116,11 @@
           <t>Foreign exchange loss</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
         <v>-0.008692999999999999</v>
       </c>
@@ -4781,7 +4207,11 @@
           <t>Net loss and comprehensive loss</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>-1.182098</v>
       </c>

--- a/output/pdf_financials_xlsx/PAU.xlsx
+++ b/output/pdf_financials_xlsx/PAU.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/PAU.xlsx
+++ b/output/pdf_financials_xlsx/PAU.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -2631,7 +2631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4296,22 +4296,117 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>30,000        $                              413,280                                                937,698                        Total                                         Equity              2,876,521   2,412,850   1,906,754                  (1,472,107)   6,137,298   6,741,370   1,181,786                                (2,351,049)    12,677,103                                                                            Shareholders’</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>– basic and diluted</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" s="5" t="n">
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" s="5" t="n">
         <v>83.798884</v>
       </c>
-      <c r="F55" s="5" t="n">
+      <c r="F56" s="5" t="n">
         <v>106.680461</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>$                       224,100                                       413,280                        Total                                         Equity                 2,613,843   1,220,676                  (1,182,098)   2,876,521   2,412,850   1,906,754                  (1,472,107)   6,137,298                                                                            Shareholders’</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>net             net                                                                                  The</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Changes                                       2022                 2023                      2024 ofCORP. Dollars) placement, loss placement, loss 31,</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/PAU.xlsx
+++ b/output/pdf_financials_xlsx/PAU.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>9.7e-05</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00072</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000891</v>
       </c>
     </row>
     <row r="13">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.182098</v>
+        <v>-1.182195</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.472107</v>
+        <v>-1.472827</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.351049</v>
+        <v>-2.35194</v>
       </c>
     </row>
     <row r="28">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.182098</v>
+        <v>-1.182195</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.472107</v>
+        <v>-1.472827</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.351049</v>
+        <v>-2.35194</v>
       </c>
     </row>
     <row r="30">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
